--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/21_Anlage_F1_und_Sicherheitenabrechnung.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/21_Anlage_F1_und_Sicherheitenabrechnung.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F-1_Stand_31_01_2024" sheetId="1" r:id="R5d9a22db2a3f4c56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hauptforderung_15_09" sheetId="2" r:id="R0378b279d27b4c37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sicherheiten_22_10" sheetId="3" r:id="Rfa9ec84c0e694124"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zahlungseingaenge" sheetId="4" r:id="R3e75475bd5ee4504"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontrolle_offene_Punkte" sheetId="5" r:id="R625158791f094120"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F-1_Stand_31_01_2024" sheetId="1" r:id="R95c9112bf5b14939"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hauptforderung_15_09" sheetId="2" r:id="R219833247eaf45b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sicherheiten_22_10" sheetId="3" r:id="Rc81964aaf0494552"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zahlungseingaenge" sheetId="4" r:id="Rc9cde61e124244bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontrolle_offene_Punkte" sheetId="5" r:id="R250b97cdf37e497b"/>
   </x:sheets>
 </x:workbook>
 </file>
